--- a/simulations/correction_peat_market/AS_taux de tri/AS_neg_inv_all.xlsx
+++ b/simulations/correction_peat_market/AS_taux de tri/AS_neg_inv_all.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\simulations\correction_peat_market\AS_taux de tri\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C05D36-E58A-46A9-B502-0DC9F9499CD7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B51F8408-095F-430F-8B6C-7C31C03CC769}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="results" sheetId="1" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <calcPr calcId="191029"/>
 </workbook>
@@ -454,6 +455,35 @@
           </cell>
           <cell r="AO5">
             <v>0.78365569398700308</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="results"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="AK3">
+            <v>-651101.69874275697</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="AL4">
+            <v>-684134.54392147798</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="AM5">
+            <v>-6.3578543683243343</v>
           </cell>
         </row>
       </sheetData>
@@ -747,7 +777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="48" max="48" width="11.90625" customWidth="1"/>
@@ -1924,6 +1954,20 @@
         <v>100.00999999999999</v>
       </c>
     </row>
+    <row r="11" spans="1:52" x14ac:dyDescent="0.35">
+      <c r="AK11" s="4">
+        <f>(AK3-[2]results!$AK$3)/[2]results!$AK$3</f>
+        <v>-0.71006743263937744</v>
+      </c>
+      <c r="AL11" s="4">
+        <f>(AL4-[2]results!$AL$4)/[2]results!$AL$4</f>
+        <v>-0.76799602109595044</v>
+      </c>
+      <c r="AM11" s="4">
+        <f>(AM5-[2]results!$AM$5)/[2]results!$AM$5</f>
+        <v>-0.87001174497548051</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B1:C1"/>
